--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -19002,10 +19002,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119669612</v>
+        <v>119669616</v>
       </c>
       <c r="B147" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -19014,25 +19014,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -19104,10 +19104,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119669616</v>
+        <v>119669612</v>
       </c>
       <c r="B148" t="n">
-        <v>97907</v>
+        <v>91185</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -19116,25 +19116,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558076.2688743499</v>
+        <v>558076</v>
       </c>
       <c r="R2" t="n">
-        <v>6274063.569206025</v>
+        <v>6274064</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2000-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557877.4740622205</v>
+        <v>557877</v>
       </c>
       <c r="R3" t="n">
-        <v>6273961.210314493</v>
+        <v>6273961</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>2000-05-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2000-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103128</v>
+        <v>103134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103128</v>
+        <v>103134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103134</v>
+        <v>103136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103134</v>
+        <v>103136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103136</v>
+        <v>103163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103136</v>
+        <v>103163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103163</v>
+        <v>103169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103163</v>
+        <v>103169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103169</v>
+        <v>103176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103169</v>
+        <v>103176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103176</v>
+        <v>103180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103176</v>
+        <v>103180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103180</v>
+        <v>103187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103180</v>
+        <v>103187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103190</v>
+        <v>103195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103190</v>
+        <v>103195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103195</v>
+        <v>103203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103195</v>
+        <v>103203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6818-2021 artfynd.xlsx
+++ b/artfynd/A 6818-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026227</v>
       </c>
       <c r="B2" t="n">
-        <v>103203</v>
+        <v>103213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75026231</v>
       </c>
       <c r="B3" t="n">
-        <v>103203</v>
+        <v>103213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
